--- a/public/sap-reporting/expansion-150-downloads/EXT-PM07-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PM07-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R2e999eb3546e4024"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R5ab4e7618f1d4f43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R41d0e8ac389d4503"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rb311741098cc4ad7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rd7c2e1d4aef34dd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Re0ba5ecde7f24ba9"/>
   </x:sheets>
 </x:workbook>
 </file>
